--- a/banks/COUTTS FINANCIALS.xlsx
+++ b/banks/COUTTS FINANCIALS.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,18 +197,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Coutts &amp; Company — Cash Flow Summary by Year</a:t>
+              <a:t>Coutts &amp; Company — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -235,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -259,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -283,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -307,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -350,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -390,13 +395,583 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Coutts &amp; Company — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Coutts &amp; Company — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$22:$AD$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Coutts &amp; Company — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$28:$AL$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$29:$AL$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -428,30 +1003,30 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -461,30 +1036,30 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -494,30 +1069,30 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q8</f>
+              <f>'Overview'!AO8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$8:$V$8</f>
+              <f>'Overview'!$AP$8:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,30 +1102,30 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q9</f>
+              <f>'Overview'!AO9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$9:$V$9</f>
+              <f>'Overview'!$AP$9:$AT$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -582,8 +1157,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -622,12 +1197,12 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -637,9 +1212,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -649,19 +1224,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>84</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>128</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -959,7 +1600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:AT38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -982,6 +1623,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -994,14 +1659,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (£m)</t>
+          <t>Balance Sheet Summary (£m)</t>
         </is>
       </c>
     </row>
@@ -1061,27 +1726,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1090,252 +1755,252 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash flows from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>-1503</v>
+        <v>61695</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>8013</v>
+        <v>62860</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2345</v>
+        <v>55573</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6242</v>
+        <v>54270</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>16461</v>
+        <v>46915</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash flows from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>16461</v>
+        <v>46915</v>
       </c>
       <c r="K6" t="n">
-        <v>6242</v>
+        <v>54270</v>
       </c>
       <c r="L6" t="n">
-        <v>2345</v>
+        <v>55573</v>
       </c>
       <c r="M6" t="n">
-        <v>8013</v>
+        <v>62860</v>
       </c>
       <c r="N6" t="n">
-        <v>-1503</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>61695</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AP6" t="n">
         <v>11.9</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>11.8</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AR6" t="n">
         <v>11.3</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AS6" t="n">
         <v>11.3</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AT6" t="n">
         <v>11.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash flows from investing activities</t>
+          <t>Loans to customers - amortised cost</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>22</v>
+        <v>18642</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>9</v>
+        <v>18034</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>36</v>
+        <v>18333</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-293</v>
+        <v>18934</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-12</v>
+        <v>17388</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash flows from investing activities</t>
+          <t>Loans to customers - amortised cost</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-12</v>
+        <v>17388</v>
       </c>
       <c r="K7" t="n">
-        <v>-293</v>
+        <v>18934</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>18333</v>
       </c>
       <c r="M7" t="n">
-        <v>9</v>
+        <v>18034</v>
       </c>
       <c r="N7" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>18642</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AP7" t="n">
         <v>13.9</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>14.3</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
         <v>13.6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AS7" t="n">
         <v>13.6</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AT7" t="n">
         <v>13.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Net cash flows from financing activities</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-258</v>
+        <v>42642</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-361</v>
+        <v>42318</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-347</v>
+        <v>37549</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-139</v>
+        <v>41057</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>123</v>
+        <v>36971</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Net cash flows from financing activities</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>123</v>
+        <v>36971</v>
       </c>
       <c r="K8" t="n">
-        <v>-139</v>
+        <v>41057</v>
       </c>
       <c r="L8" t="n">
-        <v>-347</v>
+        <v>37549</v>
       </c>
       <c r="M8" t="n">
-        <v>-361</v>
+        <v>42318</v>
       </c>
       <c r="N8" t="n">
-        <v>-258</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>42642</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="AP8" t="n">
         <v>16.4</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AQ8" t="n">
         <v>16.7</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AR8" t="n">
         <v>16.4</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AS8" t="n">
         <v>16.4</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AT8" t="n">
         <v>16.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at 31 December</t>
+          <t>Owners' equity</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>42482</v>
+        <v>1544</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>44222</v>
+        <v>1497</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>36561</v>
+        <v>1618</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>34528</v>
+        <v>1600</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>28694</v>
+        <v>1521</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at 31 December</t>
+          <t>Owners' equity</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28694</v>
+        <v>1521</v>
       </c>
       <c r="K9" t="n">
-        <v>34528</v>
+        <v>1600</v>
       </c>
       <c r="L9" t="n">
-        <v>36561</v>
+        <v>1618</v>
       </c>
       <c r="M9" t="n">
-        <v>44222</v>
+        <v>1497</v>
       </c>
       <c r="N9" t="n">
-        <v>42482</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>1544</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="AQ9" t="n">
         <v>7.7</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AR9" t="n">
         <v>7.4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AS9" t="n">
         <v>7.5</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AT9" t="n">
         <v>7.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Pillar 3 Key Metrics</t>
+          <t>Profit &amp; Loss Summary (£m)</t>
         </is>
       </c>
     </row>
@@ -1370,133 +2035,787 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>990</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>882</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>959</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>922</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>632</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>632</v>
+      </c>
+      <c r="S13" t="n">
+        <v>922</v>
+      </c>
+      <c r="T13" t="n">
+        <v>959</v>
+      </c>
+      <c r="U13" t="n">
+        <v>882</v>
+      </c>
+      <c r="V13" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-639</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-639</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-575</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-533</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-448</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-448</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-533</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-575</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-639</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-639</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>259</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>294</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>247</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>181</v>
+      </c>
+      <c r="S15" t="n">
+        <v>247</v>
+      </c>
+      <c r="T15" t="n">
+        <v>294</v>
+      </c>
+      <c r="U15" t="n">
+        <v>198</v>
+      </c>
+      <c r="V15" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1497</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1618</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1521</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1456</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>1456</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1521</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1618</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year, net of tax</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>294</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>247</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>182</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year, net of tax</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>182</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>247</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>294</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>196</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-213</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-317</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-276</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-168</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-117</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-168</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-276</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-317</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-213</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1544</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1497</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1618</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1521</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>1521</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1618</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1497</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-1503</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>8013</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>2345</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>6242</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>16461</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>16461</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>6242</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>2345</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>8013</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-1503</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flows from investing activities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-293</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Net cash flows from investing activities</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-293</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-258</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-361</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-347</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-139</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Net cash flows from financing activities</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>123</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>-139</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>-347</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>-361</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-258</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at 31 December</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>42482</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>44222</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>36561</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>34528</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>28694</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at 31 December</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>28694</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>34528</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>36561</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>44222</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>42482</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Pillar 3 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>11.4%</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>11.3%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>11.3%</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>11.8%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>11.9%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>13.5%</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>13.6%</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>13.6%</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>14.3%</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>13.9%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>16.3%</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>16.4%</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>16.4%</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>16.4%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>7.6%</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>7.5%</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>7.4%</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>7.7%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="n"/>
-    </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="F36" s="6" t="n"/>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Note: LCR/NSFR/MREL omitted from this chart - not disclosed at Coutts's own entity level in any year (see the individual sheets). Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page.</t>
         </is>
@@ -1504,7 +2823,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A38:F38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1512,6 +2831,661 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coutts &amp; Company — Tier 1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>13.6%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>13.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
+FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
+Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
+BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
+In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coutts &amp; Company — Total Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total regulatory capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1788</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1732</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1739</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1790</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
+FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
+Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
+BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
+In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coutts &amp; Company — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>16.3%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
+FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
+Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
+BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
+In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coutts &amp; Company — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>10982</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>10564</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>10591</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>10722</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>10367</v>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
+FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
+Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
+BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
+In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coutts &amp; Company — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Entity-level basis, £m. See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>RWA by risk category</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>9416</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>9231</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>9420</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>9664</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>9284</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Market risk</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1545</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1308</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>1168</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1043</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Total RWAs</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>10982</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>10564</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>10591</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>10722</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>10367</v>
+      </c>
+    </row>
+    <row r="11" ht="200" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section (Capital, RWAs and leverage table), Companies House filings:
+FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023/FY2022: Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021 (used for the FY2021 column): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+Every year's Total RWAs figure here ties exactly to the existing Total RWAs sheet; FY2022's own comparative figures (as republished in the FY2023 report) match FY2022's own originally-published figures exactly - no restatement found.
+Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
+BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
+In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A11:F11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1632,7 +3606,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1753,7 +3727,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1874,7 +3848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2001,6 +3975,1804 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coutts &amp; Company — Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Entity-level basis, £m. See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and balances at central banks</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Loans to banks - amortised cost</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Loans to customers - amortised cost</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>18642</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>18034</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>18333</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>18934</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>17388</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Amount due from holding companies and fellow subsidiaries</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>42546</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>44307</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>36623</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>34681</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>28682</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Derivatives</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Investment in group undertakings</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>354</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>367</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>383</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>413</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>61695</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>62860</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>55573</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>54270</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>46915</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Bank deposits</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Customer deposits</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>42642</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>42318</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>37549</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>41057</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>36971</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Amount due to holding companies and fellow subsidiaries</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>17306</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>18868</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>16243</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>11349</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>8291</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Derivatives</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>191</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>158</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>60151</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>61363</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>53955</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>52670</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>45394</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Owners' equity</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1544</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1497</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1618</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>61695</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>62860</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>55573</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>54270</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>46915</v>
+      </c>
+    </row>
+    <row r="24" ht="260" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's own Statement of Comprehensive Income / Balance Sheet / Statement of Changes in Equity, from its audited Companies House filings:
+FY2025/FY2024: Annual Report and Accounts 2025, pp.53-55 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023/FY2022: Annual Report and Accounts 2023, pp.50-52 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021 (used for the FY2021 column - the only source available for FY2021): Annual Report and Accounts 2022, pp.53-55 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+All figures reconcile exactly across all 5 years - every year's own closing Owners' equity ties to the next year's opening balance and to that year's own Balance Sheet Total equity figure, with no plug row needed anywhere in the chain. FY2022's own comparative figures (as republished in the FY2023 report) match FY2022's own originally-published figures (from the FY2022 report) exactly in every case checked - no restatement found. FY2023 Called-up share capital is nil ('-') in the source, consistent with earlier years' static £41m balance - flagged as a likely OCR/transcription artifact in the source scan rather than a genuine change, since Paid-in equity/Capital contribution reserve continuity around FY2023 shows no other sign of a share capital event; not corrected, shown as reported.
+Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
+BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
+In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A24:F24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coutts &amp; Company — Statement of Comprehensive Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Entity-level basis, £m. See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest receivable</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>2404</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2450</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1861</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>934</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest payable</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-1729</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-1839</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-1160</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-225</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-72</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>675</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>611</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>701</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>709</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fees and commissions receivable</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>266</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>229</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>197</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>207</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fees and commissions payable</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-21</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-20</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-22</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-29</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Other operating income</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Non-interest income</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>315</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>271</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>213</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>990</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>882</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>959</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>922</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Staff costs</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>-235</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-213</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-196</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-176</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-150</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Premises and equipment</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-19</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-13</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-36</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>-34</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>-34</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-38</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Other administrative expenses</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>-351</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>-379</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>-329</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-316</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-243</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>-639</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-639</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-575</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-533</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-448</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Profit before impairments</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>351</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>243</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>384</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>389</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Impairment (losses)/releases</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-31</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Operating profit before tax</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>262</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>381</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>358</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Tax charge</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>-87</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>-64</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-87</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-111</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>259</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>294</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>247</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(losses) after tax</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year, net of tax</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>294</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>247</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="29" ht="260" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's own Statement of Comprehensive Income / Balance Sheet / Statement of Changes in Equity, from its audited Companies House filings:
+FY2025/FY2024: Annual Report and Accounts 2025, pp.53-55 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023/FY2022: Annual Report and Accounts 2023, pp.50-52 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021 (used for the FY2021 column - the only source available for FY2021): Annual Report and Accounts 2022, pp.53-55 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+All figures reconcile exactly across all 5 years - every year's own closing Owners' equity ties to the next year's opening balance and to that year's own Balance Sheet Total equity figure, with no plug row needed anywhere in the chain. FY2022's own comparative figures (as republished in the FY2023 report) match FY2022's own originally-published figures (from the FY2022 report) exactly in every case checked - no restatement found. FY2023 Called-up share capital is nil ('-') in the source, consistent with earlier years' static £41m balance - flagged as a likely OCR/transcription artifact in the source scan rather than a genuine change, since Paid-in equity/Capital contribution reserve continuity around FY2023 shows no other sign of a share capital event; not corrected, shown as reported.
+Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
+BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
+In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coutts &amp; Company — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Entity-level basis, £m, chronological (oldest to newest). See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Called-up share capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Paid-in equity</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Cash flow hedging reserve</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Capital contribution reserve</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>At 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>382</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>833</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year (FY2021)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n">
+        <v>181</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges: amount recognised in equity (FY2021)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Paid-in equity dividends paid (FY2021)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Ordinary dividends paid (FY2021)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n">
+        <v>-105</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-105</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>382</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>897</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year (FY2022)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n">
+        <v>247</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Paid-in equity redeemed (FY2022)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>-165</v>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n">
+        <v>-165</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Paid-in equity issued (FY2022)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges: amount recognised in equity (FY2022)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges: amount transferred from equity to earnings (FY2022)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges: tax (FY2022)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Paid-in equity dividends paid (FY2022)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n">
+        <v>-16</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Ordinary dividends paid (FY2022)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n">
+        <v>-225</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-225</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Redemption of paid-in equity, gross (FY2022)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>382</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>901</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year (FY2023)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n">
+        <v>294</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Paid-in equity redeemed (FY2023)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n">
+        <v>-35</v>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges: amount recognised in equity (FY2023)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges: amount transferred from equity to earnings (FY2023)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Paid-in equity dividends paid (FY2023)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n">
+        <v>-31</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>-31</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Ordinary dividends paid (FY2023)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n">
+        <v>-210</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-210</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>382</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>954</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year (FY2024)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n">
+        <v>198</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges: amount recognised in equity (FY2024)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges: reclassification of OCI to P&amp;L (FY2024)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges: tax (FY2024)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Paid-in equity dividends paid (FY2024)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n">
+        <v>-28</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Ordinary dividends paid (FY2024)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n">
+        <v>-289</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-289</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>382</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>835</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year (FY2025)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n">
+        <v>259</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges: reclassification of OCI to P&amp;L (FY2025)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Paid-in equity dividends paid (FY2025)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n">
+        <v>-26</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>-26</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Ordinary dividends paid (FY2025)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n">
+        <v>-187</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>-187</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>382</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>881</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="40" ht="260" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's own Statement of Comprehensive Income / Balance Sheet / Statement of Changes in Equity, from its audited Companies House filings:
+FY2025/FY2024: Annual Report and Accounts 2025, pp.53-55 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023/FY2022: Annual Report and Accounts 2023, pp.50-52 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021 (used for the FY2021 column - the only source available for FY2021): Annual Report and Accounts 2022, pp.53-55 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+All figures reconcile exactly across all 5 years - every year's own closing Owners' equity ties to the next year's opening balance and to that year's own Balance Sheet Total equity figure, with no plug row needed anywhere in the chain. FY2022's own comparative figures (as republished in the FY2023 report) match FY2022's own originally-published figures (from the FY2022 report) exactly in every case checked - no restatement found. FY2023 Called-up share capital is nil ('-') in the source, consistent with earlier years' static £41m balance - flagged as a likely OCR/transcription artifact in the source scan rather than a genuine change, since Paid-in equity/Capital contribution reserve continuity around FY2023 shows no other sign of a share capital event; not corrected, shown as reported.
+Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
+BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
+In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A40:G40"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2936,16 +6708,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2956,79 +6728,661 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — CET1 Capital</t>
+          <t>Coutts &amp; Company — Asset Quality</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>Entity-level basis, £m. See source note at bottom.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (£m)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (£m)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (£m)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (£m)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 (£m)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1248</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1192</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1199</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1260</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
-FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Loans - amortised cost and FVOCI, by IFRS 9 stage</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>17334</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>16998</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>17400</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>18112</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>16648</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1110</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>840</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>906</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>795</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>338</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>317</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>247</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Inter-Group (classified Stage 1)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>42464</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>44301</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>36633</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>34681</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>28678</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Total gross loans (amortised cost and FVOCI)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>61246</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>62456</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>55186</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>53818</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>46512</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ECL provisions, by IFRS 9 stage</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Inter-Group</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Total ECL provisions</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>ECL provisions coverage</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>1.17%</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>2.21%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>2.88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 (%)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>14.79%</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>11.67%</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>12.96%</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>14.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Inter-Group (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Overall coverage (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>ECL charge/(release) for the year, by IFRS 9 stage</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-44</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Inter-Group</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-8</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Total ECL charge/(release) for the year</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-19</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-57</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Amounts written off</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Derived ratio</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 / gross third-party loans (excl. Inter-Group)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>1.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="220" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's own Note 8 'Loan impairment provisions', Companies House filings:
+FY2025/FY2024: Annual Report and Accounts 2025, p.69 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023/FY2022: Annual Report and Accounts 2023, p.65 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021 (used for the FY2021 column): Annual Report and Accounts 2022, p.68 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+'Inter-Group' is loans/placements with holding companies and fellow subsidiaries (dominant on this entity's balance sheet - see Amount due from holding companies and fellow subsidiaries on the Balance Sheet) - classified Stage 1 by the Bank's own convention and shown as its own row here, not blended into the third-party Stage 1/2/3 split. FY2022's own comparative figures (as republished in the FY2023 report) match FY2022's own originally-published figures exactly - no restatement found. The derived 'Stage 3 / gross third-party loans' ratio below excludes Inter-Group from the denominator, since inter-group placements carry negligible credit risk and would otherwise dilute the third-party asset-quality signal.
 Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
 BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
 In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
@@ -3037,348 +7391,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Coutts &amp; Company — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>CET1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>11.4%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>11.3%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>11.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>11.8%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>11.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
-FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
-Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
-BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
-In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Coutts &amp; Company — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1488</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1432</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1439</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1535</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1437</v>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
-FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
-Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
-BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
-In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Coutts &amp; Company — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>13.5%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>13.6%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>13.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>13.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
-FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
-Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
-BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
-In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A32:F32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3404,7 +7417,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — Total Capital</t>
+          <t>Coutts &amp; Company — CET1 Capital</t>
         </is>
       </c>
     </row>
@@ -3450,23 +7463,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total regulatory capital</t>
+          <t>Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1788</v>
+        <v>1248</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>1732</v>
+        <v>1192</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1739</v>
+        <v>1199</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1790</v>
+        <v>1260</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1703</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">
@@ -3511,7 +7524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — Total Capital Ratio</t>
+          <t>Coutts &amp; Company — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -3557,32 +7570,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
+          <t>CET1 ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>11.9%</t>
         </is>
       </c>
     </row>
@@ -3628,7 +7641,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — Total RWAs</t>
+          <t>Coutts &amp; Company — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -3674,23 +7687,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted assets</t>
+          <t>Tier 1 capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>10982</v>
+        <v>1488</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>10564</v>
+        <v>1432</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>10591</v>
+        <v>1439</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>10722</v>
+        <v>1535</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>10367</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">

--- a/banks/COUTTS FINANCIALS.xlsx
+++ b/banks/COUTTS FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2850,14 +2851,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — Tier 1 Ratio</t>
+          <t>Coutts &amp; Company — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -2896,33 +2897,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>13.5%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>13.6%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>13.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>13.9%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1488</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1432</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1439</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1535</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1437</v>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">
@@ -2967,14 +2958,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — Total Capital</t>
+          <t>Coutts &amp; Company — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -3013,23 +3004,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total regulatory capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1788</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1732</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1739</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1790</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1703</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>13.6%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>13.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">
@@ -3074,14 +3075,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — Total Capital Ratio</t>
+          <t>Coutts &amp; Company — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -3120,33 +3121,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>16.3%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>16.4%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.4%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>16.4%</t>
-        </is>
+          <t>Total regulatory capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1788</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1732</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1739</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1790</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1703</v>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">
@@ -3191,14 +3182,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — Total RWAs</t>
+          <t>Coutts &amp; Company — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -3237,23 +3228,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted assets</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>10982</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>10564</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>10591</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>10722</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>10367</v>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>16.3%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">
@@ -3279,6 +3280,113 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coutts &amp; Company — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>10982</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>10564</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>10591</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>10722</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>10367</v>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
+FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
+Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
+BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
+In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3485,7 +3593,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3584,127 +3692,6 @@
       </c>
     </row>
     <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
-FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
-Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
-BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
-In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Coutts &amp; Company — LCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>LCR</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Not publicly disclosed at Coutts's own entity level in any year - managed and disclosed only at the UK DoLSub sub-group level (NatWest Bank Plc + RBS plc + Coutts). See the sheet's source note for the exact quoted basis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
@@ -3747,7 +3734,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — NSFR</t>
+          <t>Coutts &amp; Company — LCR</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3776,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>NSFR</t>
+          <t>LCR</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3868,6 +3855,127 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Coutts &amp; Company — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>NSFR</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Not publicly disclosed at Coutts's own entity level in any year - managed and disclosed only at the UK DoLSub sub-group level (NatWest Bank Plc + RBS plc + Coutts). See the sheet's source note for the exact quoted basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
+FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
+Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
+BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
+In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>Coutts &amp; Company — MREL Ratio</t>
         </is>
       </c>
@@ -7403,10 +7511,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -7417,21 +7525,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — CET1 Capital</t>
+          <t>Coutts &amp; Company — KM1 Key Metrics</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>Coutts &amp; Company's own entity-level 'UK KM1: Key metrics' template, reproduced whole in its own row order, row numbers, labels and precision. Amounts in £m, ratios as printed. FY2025-FY2022 are each from that year's OWN Pillar 3 report; FY2021 is the FY2022 report's comparative column, because no Coutts-specific FY2021 Pillar 3 report exists. Rows 15-20 and UK 14a-14e are blank by formal exclusion, not for want of data - see source note.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -7461,35 +7569,806 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (amounts)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1  Common equity tier 1 (CET1) capital (£m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>1248</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C5" s="6" t="n">
         <v>1192</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D5" s="6" t="n">
         <v>1199</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E5" s="6" t="n">
         <v>1260</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>1235</v>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
-FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2  Tier 1 capital (£m)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1488</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1432</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1439</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1535</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3  Total capital (£m)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1788</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1732</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1739</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1790</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure amounts</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4  Total risk-weighted exposure amount (£m)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>10982</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>10564</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>10591</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>10722</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>10367</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Capital ratios (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>5  Common equity tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>6  Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>13.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7  Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements based on SREP (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>UK 7a  Additional CET1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>UK 7b  Additional AT1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>UK 7c  Additional Tier 2 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>UK 7d  Total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>8  Capital conservation buffer (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>9  Institution specific countercyclical capital buffer (%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>11  Combined buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>UK 11a  Overall capital requirements (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>12  CET1 available after meeting the total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>13  Total exposure measure excluding claims on central banks (£m)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>19649</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>19022</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>19358</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>20022</v>
+      </c>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>14  Leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Additional leverage ratio disclosure requirements (blank in every edition: Coutts &amp; Co is not an LREQ firm)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>UK 14a  Fully loaded ECL accounting model leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>UK 14b  Leverage ratio including claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>UK 14c  Average leverage ratio excluding claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>UK 14d  Average leverage ratio including claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>UK 14e  Countercyclical leverage ratio buffer (%)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity coverage ratio (blank in every edition: managed and disclosed at UK DoLSub sub-group level under the DoLSub waiver, not at entity level)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>15  Total high-quality liquid assets (HQLA) (weighted value-average) (£m)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>UK 16a  Cash outflows - Total weighted value (£m)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>UK 16b  Cash inflows - Total weighted value (£m)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>16  Total net cash outflows (adjusted value) (£m)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>17  Liquidity coverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Net stable funding ratio (blank in every edition: same UK DoLSub waiver basis)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>18  Total available stable funding (£m)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>19  Total required stable funding (£m)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>20  NSFR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+    </row>
+    <row r="45" ht="330" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's OWN entity-level 'UK KM1: Key metrics' template, reproduced whole in the Bank's own row order, row numbers, labels and precision. Amounts in £m, ratios exactly as printed:
+FY2025: Coutts &amp; Co Pillar 3 Report 2025, p.8 (31 December 2025 column) - https://investors.natwestgroup.com/~/media/Files/R/RBS-IR-V2/results-center/13022026/coutts-co-pillar-3-report.pdf
+FY2024: Coutts &amp; Co Pillar 3 Report 2024, p.7 (31 December 2024 column) - https://investors.natwestgroup.com/~/media/Files/R/RBS-IR-V2/results-center/14022025/coutts-pillar-3-report.pdf
+FY2023: Coutts &amp; Co Pillar 3 Report 2023, p.7 (31 December 2023 column) - https://investors.natwestgroup.com/~/media/Files/R/RBS-IR-V2/results-center/16022024/coutts-co-pillar-3-report.pdf
+FY2022: Coutts &amp; Co Pillar 3 Report 2022, p.7 (31 December 2022 column) - https://investors.natwestgroup.com/~/media/Files/R/RBS-IR-V2/results-center/17022023/coutts-co-pillar-3-report.pdf
+FY2021: NO COUTTS-SPECIFIC PILLAR 3 REPORT EXISTS FOR FY2021 - the earliest Coutts &amp; Co Pillar 3 document published on the NatWest Group investor site is the half-year 2022 supplement (29 July 2022), and the FY2022 report above is the first full-year one. The FY2021 column here is therefore taken from the FY2022 report's own '31 December 2021' COMPARATIVE COLUMN, which that report's 'Presentation of Information' section states is its standard comparative period ('Where a comparative is not prescribed, the comparative period provided is December 2021') - https://investors.natwestgroup.com/~/media/Files/R/RBS-IR-V2/results-center/17022023/coutts-co-pillar-3-report.pdf
+SOURCE-SET CORRECTION (2026-09-17). This Pillar 3 document set was NOT previously cited anywhere in this workbook: the other Pillar 3 sheets here are sourced from Coutts's own Annual Report 'Risk and capital management' section at Companies House. Coutts &amp; Company does publish its own standalone, entity-level Pillar 3 reports - quarterly, on the NatWest Group investor-relations site rather than its own - and they carry a full UK KM1. They were located by enumerating investors.natwestgroup.com's results centre; natwestgroup.com's own sitemap lists no Pillar 3 page and coutts.com's lists none either, which is why earlier searches of the obvious domains found nothing. The figures agree with the Annual-Report-sourced figures already on the other sheets in every year and every row cross-checked.
+ROWS 15-20 (LCR AND NSFR) ARE BLANK IN EVERY EDITION, AND THIS IS A FORMAL EXCLUSION RATHER THAN A DATA GAP. Each report footnotes the block: 'Under the UK DoLSub waiver Coutts &amp; Co liquidity and funding are managed and disclosed at the sub-group level rather than entity level.' The 'Presentation of Information' section adds that 'The liquidity disclosures completed at UK Domestic Liquidity Subgroup (UK DoLSub) level are published in the NatWest Holdings Group Pillar 3 report. The UK DoLSub waiver allows NWB Plc, RBS plc and Coutts &amp; Co to manage liquidity as a single sub-group rather than at an entity level.' The NatWest Holdings Group figure is a THREE-ENTITY SUB-GROUP figure and is deliberately NOT substituted for Coutts's own, which would be a basis error.
+ROWS UK 14a-14e ARE LIKEWISE A FORMAL EXCLUSION: 'Coutts &amp; Co is not an LREQ firm, therefore not subject to the additional leverage ratio disclosure requirements.'
+ROWS UK 8a, UK 9a, 10 AND UK 10a ARE NOT PRINTED AT ALL in any edition - each report lists them by name and says they are omitted as zero / not applicable - so they are omitted here too rather than shown as zeros.
+ROWS 13 AND 14 ARE BLANK FOR FY2021 SPECIFICALLY: the FY2022 report's KM1 prints leverage figures for its four 2022 columns only and leaves the 31 December 2021 cell empty. That is a blank in the comparative itself, not an omission here.
+ROW 9 FY2021 IS A PRINTED ZERO ('0.0'), not a dash, and is recorded as a zero - the UK countercyclical buffer rate was genuinely 0% at 31 December 2021 and was reset to 1% during 2022 and 2% from July 2023.
+LEVEL OF APPLICATION (the basis on which these disclosures are owed): 'Coutts &amp; Co being a large, non-listed subsidiary of NatWest Group is subject to a reduced number of disclosures as set out in the Level of Application chapter in the Disclosure (CRR) part of the PRA Rulebook.' NatWest Group defines its large subsidiaries as those designated O-SII by the PRA or with total assets of €30bn or more.
+LATEST-EDITION CHECK (2026-09-17): the NatWest Group results centre was enumerated in full. Coutts's newest FULL-YEAR Pillar 3 is the 2025 report used here (published 13 February 2026), so this workbook is current. Coutts also publishes Q1, half-year and Q3 reports - the newest of any kind is the half-year 2026 report (12 August 2026) - but this workbook is annual, so no interim edition is used.
 Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
 BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
 In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
@@ -7498,7 +8377,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A45:F45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7524,14 +8403,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — CET1 Ratio</t>
+          <t>Coutts &amp; Company — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -7570,33 +8449,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>CET1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>11.4%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>11.3%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>11.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>11.8%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>11.9%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1248</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1192</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1235</v>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">
@@ -7641,14 +8510,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — Tier 1 Capital</t>
+          <t>Coutts &amp; Company — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -7687,23 +8556,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1488</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1432</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1439</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1535</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1437</v>
+          <t>CET1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>11.4%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>11.3%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>11.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>11.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>11.9%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">

--- a/banks/COUTTS FINANCIALS.xlsx
+++ b/banks/COUTTS FINANCIALS.xlsx
@@ -3599,7 +3599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3607,7 +3607,6 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3650,11 +3649,6 @@
           <t>FY2022</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3682,7 +3676,6 @@
           <t>7.7%</t>
         </is>
       </c>
-      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -3707,8 +3700,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/COUTTS FINANCIALS.xlsx
+++ b/banks/COUTTS FINANCIALS.xlsx
@@ -1664,6 +1664,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3774,27 +3775,27 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
     </row>
@@ -3895,27 +3896,27 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
     </row>
@@ -4016,27 +4017,27 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
         </is>
       </c>
     </row>

--- a/banks/COUTTS FINANCIALS.xlsx
+++ b/banks/COUTTS FINANCIALS.xlsx
@@ -116,7 +116,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F36" s="6" t="n"/>
     </row>
-    <row r="38" ht="45" customHeight="1">
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Note: LCR/NSFR/MREL omitted from this chart - not disclosed at Coutts's own entity level in any year (see the individual sheets). Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page.</t>
@@ -2917,7 +2917,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="338" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
@@ -3034,7 +3034,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="338" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
@@ -3141,7 +3141,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="338" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
@@ -3258,7 +3258,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="338" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
@@ -3365,7 +3365,7 @@
         <v>10367</v>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="338" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
@@ -3572,7 +3572,7 @@
         <v>10367</v>
       </c>
     </row>
-    <row r="11" ht="200" customHeight="1">
+    <row r="11" ht="273" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section (Capital, RWAs and leverage table), Companies House filings:
@@ -3600,7 +3600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3620,7 +3620,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m / %</t>
         </is>
       </c>
     </row>
@@ -3678,15 +3678,117 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 not disclosed - the FY2022 Annual Report (the only source for FY2021) does not include a leverage ratio table at all; the leverage-ratio disclosure only begins from the FY2023 report onward (shown there with a FY2022 comparative, used for the FY2022 column here).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total exposure measure including claims on central banks (£m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>19652</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>19025</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>19361</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>20025</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Claims on central banks excluded (£m)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Total exposure measure excluding claims on central banks (£m)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>19649</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>19022</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>19358</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>20022</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Leverage ratio including claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>7.4%</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="351" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 not disclosed - the FY2022 Annual Report (the only source for FY2021) does not include a leverage ratio table at all; the leverage-ratio disclosure only begins from the FY2023 report onward (shown there with a FY2022 comparative, used for the FY2022 column here).
+BOTH LEVERAGE BASES NOW CARRIED, FY2022-FY2025 - ADDED 2026-10-09 (GA-026). Template UK LR2 (LRCom) prints BOTH measures: row 24 and UK-25c on the INCLUDING-claims-on-central-banks basis, UK-24b and 25 on the EXCLUDING basis, with the reconciling deduction at UK-24a. Until today this sheet carried a single 'UK leverage ratio' row and did not say which basis it was; it is the EXCLUDING one, and it keeps its place FIRST because check_overview_ties.py reads the first cell printed as a percentage on a ratio sheet.
+THE TWO RATIOS ARE EQUAL IN EVERY YEAR AT THE PRECISION COUTTS PRINTS, AND THAT IS THE FINDING, NOT A COPYING ERROR. This bank holds almost no claims on central banks: UK-24a is £3m in all four years, against a roughly £20bn exposure measure, so the deduction moves the ratio by about 0.001pp and both rows round to the same one-decimal figure. The including rows are still added, because 'the bank publishes both measures and they coincide' is a different fact from 'the bank publishes one measure', and only the document can tell them apart.
+EACH YEAR FROM ITS OWN EDITION, template UK LR2 - LRCom 'continued', column headed 'Coutts &amp; Co', read at 300 dpi:
+  FY2025 - Coutts &amp; Co Pillar 3 Report 2025, p.22, 31 December 2025 column: row 23 1,488; row 24 19,652; UK-24a (3); UK-24b 19,649; row 25 7.6%; UK-25c 7.6%.
+  FY2024 - Coutts &amp; Co Pillar 3 Report 2024, p.22, 31 December 2024 column: row 23 1,432; row 24 19,025; UK-24a (3); UK-24b 19,022; row 25 7.5%; UK-25c 7.5%.
+  FY2023 - Coutts &amp; Co Pillar 3 Report 2023, p.22, FIRST column: row 23 1,439; row 24 19,361; UK-24a (3); UK-24b 19,358; row 25 7.4%; UK-25c 7.4%.
+  FY2022 - Coutts &amp; Co Pillar 3 Report 2022, p.20, 31 December 2022 column: row 23 1,535; row 24 20,025; UK-24a (3); UK-24b 20,022; row 25 7.7%; UK-25c 7.7%.
+THE FY2023 EDITION MISPRINTS ITS OWN COLUMN HEADINGS: page 22 heads BOTH columns '31 December 2022'. Read at 300 dpi to be sure it is the document and not the text layer. The first column is in fact 31 December 2023, and it is identified by figures rather than by its heading - its five values (1,439 / 19,361 / (3) / 19,358 / 7.4%) equal the FY2024 edition's 31 December 2023 COMPARATIVE exactly, while the second column's (1,535 / 20,025 / (3) / 20,022 / 7.7%) equal the FY2022 edition's own 31 December 2022 column exactly. Two independent cross-edition matches, so the mislabelling is certain and the assignment is not a guess. The bank's misprint is reproduced as a finding here and nothing in this workbook is relabelled to hide it.
+THE FY2022 EDITION'S SECOND COLUMN IS 30 JUNE 2022, not a year-end, and is deliberately not used (row 24 19,435; UK-24a (3); UK-24b 19,432; row 25 7.2%; UK-25c 7.2%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="91" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
+CHECKS RUN BEFORE TRANSCRIBING. (1) ENTITY: row 25 reproduces the ratio this sheet already carried in all four years (7.6% / 7.5% / 7.4% / 7.7%), so the LR2 is the same entity as the rest of the workbook. (2) CROSS-EDITION: each edition's comparative equals the next edition's own-year column to the last digit. (3) ARITHMETIC: row 24 minus UK-24a equals UK-24b in all four years. (4) RATIO TIE: row 23 over each exposure measure reproduces both printed ratios (e.g. FY2025 1,488/19,652 = 7.57% and 1,488/19,649 = 7.57%, both -&gt; 7.6%).
+FY2021 CORRECTLY GETS NOTHING on either basis - see the sentence above; and in any case the UK dual basis took effect only for periods from 1 January 2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="403" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
 FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
@@ -3700,9 +3802,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A7:E7"/>
+  <mergeCells count="3">
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3799,14 +3902,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed at Coutts's own entity level in any year - managed and disclosed only at the UK DoLSub sub-group level (NatWest Bank Plc + RBS plc + Coutts). See the sheet's source note for the exact quoted basis.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="325" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
@@ -3920,14 +4023,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed at Coutts's own entity level in any year - managed and disclosed only at the UK DoLSub sub-group level (NatWest Bank Plc + RBS plc + Coutts). See the sheet's source note for the exact quoted basis.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="325" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
@@ -4041,14 +4144,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed for any year - MREL is defined in the Annual Report's own glossary of capital concepts, but no MREL ratio for Coutts specifically is ever stated.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="325" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
@@ -4520,7 +4623,7 @@
         <v>46915</v>
       </c>
     </row>
-    <row r="24" ht="260" customHeight="1">
+    <row r="24" ht="299" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own Statement of Comprehensive Income / Balance Sheet / Statement of Changes in Equity, from its audited Companies House filings:
@@ -5113,7 +5216,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="29" ht="260" customHeight="1">
+    <row r="29" ht="299" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own Statement of Comprehensive Income / Balance Sheet / Statement of Changes in Equity, from its audited Companies House filings:
@@ -5847,7 +5950,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="40" ht="260" customHeight="1">
+    <row r="40" ht="273" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own Statement of Comprehensive Income / Balance Sheet / Statement of Changes in Equity, from its audited Companies House filings:
@@ -7477,7 +7580,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="220" customHeight="1">
+    <row r="32" ht="299" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own Note 8 'Loan impairment provisions', Companies House filings:
@@ -7505,7 +7608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -8346,7 +8449,7 @@
       <c r="E43" s="6" t="n"/>
       <c r="F43" s="6" t="n"/>
     </row>
-    <row r="45" ht="330" customHeight="1">
+    <row r="45" ht="364" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's OWN entity-level 'UK KM1: Key metrics' template, reproduced whole in the Bank's own row order, row numbers, labels and precision. Amounts in £m, ratios exactly as printed:
@@ -8361,7 +8464,14 @@
 ROWS UK 8a, UK 9a, 10 AND UK 10a ARE NOT PRINTED AT ALL in any edition - each report lists them by name and says they are omitted as zero / not applicable - so they are omitted here too rather than shown as zeros.
 ROWS 13 AND 14 ARE BLANK FOR FY2021 SPECIFICALLY: the FY2022 report's KM1 prints leverage figures for its four 2022 columns only and leaves the 31 December 2021 cell empty. That is a blank in the comparative itself, not an omission here.
 ROW 9 FY2021 IS A PRINTED ZERO ('0.0'), not a dash, and is recorded as a zero - the UK countercyclical buffer rate was genuinely 0% at 31 December 2021 and was reset to 1% during 2022 and 2% from July 2023.
-LEVEL OF APPLICATION (the basis on which these disclosures are owed): 'Coutts &amp; Co being a large, non-listed subsidiary of NatWest Group is subject to a reduced number of disclosures as set out in the Level of Application chapter in the Disclosure (CRR) part of the PRA Rulebook.' NatWest Group defines its large subsidiaries as those designated O-SII by the PRA or with total assets of €30bn or more.
+LEVEL OF APPLICATION (the basis on which these disclosures are owed): 'Coutts &amp; Co being a large, non-listed subsidiary of NatWest Group is subject to a reduced number of disclosures as set out in the Level of Application chapter in the Disclosure (CRR) part of the PRA Rulebook.' NatWest Group defines its large subsidiaries as those designated O-SII by the PRA or with total assets of €30bn or more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="330" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (2026-09-17): the NatWest Group results centre was enumerated in full. Coutts's newest FULL-YEAR Pillar 3 is the 2025 report used here (published 13 February 2026), so this workbook is current. Coutts also publishes Q1, half-year and Q3 reports - the newest of any kind is the half-year 2026 report (12 August 2026) - but this workbook is annual, so no interim edition is used.
 Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
 BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
@@ -8370,8 +8480,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A47:F47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8462,7 +8573,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="338" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
@@ -8579,7 +8690,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="338" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:

--- a/banks/COUTTS FINANCIALS.xlsx
+++ b/banks/COUTTS FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2852,14 +2853,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — Tier 1 Capital</t>
+          <t>Coutts &amp; Company — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -2898,23 +2899,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1488</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1432</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1439</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1535</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1437</v>
+          <t>CET1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>11.4%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>11.3%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>11.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>11.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>11.9%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="338" customHeight="1">
@@ -2959,14 +2970,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — Tier 1 Ratio</t>
+          <t>Coutts &amp; Company — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -3005,33 +3016,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>13.5%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>13.6%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>13.6%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>13.9%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1488</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1432</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1439</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1535</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1437</v>
       </c>
     </row>
     <row r="6" ht="338" customHeight="1">
@@ -3076,14 +3077,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — Total Capital</t>
+          <t>Coutts &amp; Company — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -3122,23 +3123,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total regulatory capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1788</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1732</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1739</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1790</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1703</v>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>13.6%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>13.6%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="338" customHeight="1">
@@ -3183,14 +3194,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — Total Capital Ratio</t>
+          <t>Coutts &amp; Company — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -3229,33 +3240,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>16.3%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>16.4%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.4%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>16.4%</t>
-        </is>
+          <t>Total regulatory capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1788</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1732</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1739</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1790</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1703</v>
       </c>
     </row>
     <row r="6" ht="338" customHeight="1">
@@ -3300,14 +3301,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — Total RWAs</t>
+          <t>Coutts &amp; Company — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -3346,23 +3347,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted assets</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>10982</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>10564</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>10591</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>10722</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>10367</v>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>16.3%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="338" customHeight="1">
@@ -3388,6 +3399,113 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coutts &amp; Company — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>10982</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>10564</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>10591</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>10722</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>10367</v>
+      </c>
+    </row>
+    <row r="6" ht="338" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
+FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
+Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
+BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
+In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3594,7 +3712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3806,127 +3924,6 @@
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A12:E12"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Coutts &amp; Company — LCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>LCR</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Not publicly disclosed at Coutts's own entity level in any year - managed and disclosed only at the UK DoLSub sub-group level (NatWest Bank Plc + RBS plc + Coutts). See the sheet's source note for the exact quoted basis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="325" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
-FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
-Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
-BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
-In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3952,7 +3949,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — NSFR</t>
+          <t>Coutts &amp; Company — LCR</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3991,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>NSFR</t>
+          <t>LCR</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -4073,7 +4070,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — MREL Ratio</t>
+          <t>Coutts &amp; Company — NSFR</t>
         </is>
       </c>
     </row>
@@ -4115,39 +4112,39 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>MREL Ratio</t>
+          <t>NSFR</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
+          <t>Not applicable – UK DoLSub waiver: Coutts Pillar 3 FY2022–25 KM1 footnote, 'Coutts &amp; Co liquidity [and funding are] managed and disclosed at the sub-group level' (FY2022 ed. covers Dec-21); see NWH Group.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed for any year - MREL is defined in the Annual Report's own glossary of capital concepts, but no MREL ratio for Coutts specifically is ever stated.</t>
+          <t>Note: Not publicly disclosed at Coutts's own entity level in any year - managed and disclosed only at the UK DoLSub sub-group level (NatWest Bank Plc + RBS plc + Coutts). See the sheet's source note for the exact quoted basis.</t>
         </is>
       </c>
     </row>
@@ -4645,6 +4642,127 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coutts &amp; Company — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL ratio in Coutts Pillar 3 FY2022–25 (KM1 has no MREL rows; CCA gives only per-instrument amounts 'for the purpose of MREL') or in ARs FY2021–25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Not publicly disclosed for any year - MREL is defined in the Annual Report's own glossary of capital concepts, but no MREL ratio for Coutts specifically is ever stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="325" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
+FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
+Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
+BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
+In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7608,6 +7726,237 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coutts &amp; Company — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>17.03%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>12.71%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>18.27%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>15.83%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>16.77%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>13.23%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>18.17%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>15.44%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>11.90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Return on Equity (RoE) (as published)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>17.3%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="260" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: TWO KINDS OF FIGURE, NEVER MERGED. The rows above are not one series. The 'Return on equity/assets' rows are THIS PROJECT'S OWN ARITHMETIC on the figures printed on this workbook's statement sheets. The rows marked '(as published)' are the bank's own published ratios, quoted verbatim, each struck on the bank's own definition - which differs from bank to bank and usually from ours, most often in whether the numerator is before or after tax and whether the denominator is average, opening or year-end equity, tangible equity or required equity. They are not averaged, reconciled, or substituted for one another, and where they disagree both stand: the disagreement is the finding.
+THE BANK'S OWN DEFINITIONS, VERBATIM. Return on Equity (RoE): “RoE is calculated using annual profit for the period divided by the average owner's equity, which at 31 December 2025 was GBP1.5 billion (2024 - GBP1.5 billion).”
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return. The two diverge most in FY2024, where return on equity is 12.71% on an average basis and 13.23% on a year-end basis.
+FY2021 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2021 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2021 because it needs only the closing balance.
+FIGURES THE BANK PUBLISHED ONLY AS A LATER EDITION'S COMPARATIVE, AND WHY THEY ARE NOT IN THE CELLS ABOVE. FY2024 Return on Equity (RoE) 13.5%. Each year's cell carries what that year's OWN annual report printed. A comparative restated in a later edition is a different claim - it may rest on a revised definition, a restated perimeter or a corrected prior figure - so it is recorded here rather than substituted into the year it refers to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “profit for the year” and the Balance Sheet rows “owners' equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from Coutts &amp; Company's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The '(as published)' rows are quoted verbatim from Coutts &amp; Company's own disclosures and are recorded, with the exact document, page and verification state for each, in research/profitability/published_returns.jsonl under ‘COUTTS’.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8483,113 +8832,6 @@
   <mergeCells count="2">
     <mergeCell ref="A45:F45"/>
     <mergeCell ref="A47:F47"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Coutts &amp; Company — CET1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1248</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1192</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1199</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1260</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="6" ht="338" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Coutts &amp; Company's own 'Risk and capital management' section, Companies House filings:
-FY2025/FY2024: Annual Report and Accounts 2025, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzUyMTA2MDcwMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023/FY2022 (capital): Annual Report and Accounts 2023, p.30 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzQyMDgzOTQ5OWFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021 (capital): Annual Report and Accounts 2022, p.34 - https://find-and-update.company-information.service.gov.uk/company/00036695/filing-history/MzM4NTMwNzEyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-LCR/NSFR/MREL are NOT disclosed at Coutts's own entity level in any year - the FY2025 report states explicitly: 'Disclosures relating to these metrics... are completed at UK DoLSub level and published in the... NatWest Holdings Group Annual Report and Accounts. Under the UK DoLSub waiver NWB Plc, RBS plc and Coutts are permitted to manage liquidity on a consolidated sub-group basis rather than individually at the entity level.' Only the regulatory minimum requirement (100%/100%) is stated, never an achieved value - this matches the RBS plc build's precedent elsewhere in this project (RBS plc + NatWest Bank plc + Coutts share one DoLSub liquidity disclosure). MREL is mentioned only as a defined concept, with no ratio ever stated for Coutts specifically.
-Coutts &amp; Company (company 00036695, FRN 122287) is a wholly-owned subsidiary of NatWest Group plc, part of the ring-fenced NatWest Holdings (NWH) Group sub-group. All figures are Coutts &amp; Company's own entity-level financial statements/disclosures, not the wider NatWest Group. A private unlimited company - voluntarily files full audited accounts at Companies House despite the unlimited-company form (which would otherwise exempt it from public filing), same as C. Hoare &amp; Co. elsewhere in this project.
-BASIS CHANGE: the FY2022 Annual Report states its financial statements 'are prepared on a standalone basis for Coutts. Previously these were prepared on a consolidated basis for Coutts and its subsidiaries.' The FY2021 figures used here are as shown in the FY2022 report's own comparative column (the only source available for FY2021) - it isn't confirmed whether that comparative was itself restated onto the new standalone basis or retains the original consolidated FY2021 basis. Flagged, not resolved.
-In September 2022 Coutts acquired the 'Adam &amp; Company' private-banking business from The Royal Bank of Scotland plc (a Part VII-style transfer) - RBS plc is a separate entity already built in this project; that acquisition is the source-side counterpart of this project's earlier RBS plc entity-identity finding.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8615,14 +8857,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coutts &amp; Company — CET1 Ratio</t>
+          <t>Coutts &amp; Company — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m</t>
         </is>
       </c>
     </row>
@@ -8661,33 +8903,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>CET1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>11.4%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>11.3%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>11.3%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>11.8%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>11.9%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1248</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1192</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1235</v>
       </c>
     </row>
     <row r="6" ht="338" customHeight="1">
